--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_special_lines.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.455</v>
+        <v>0.367</v>
       </c>
       <c r="G2">
-        <v>0.01306265080289541</v>
+        <v>-0.02093002889920308</v>
       </c>
       <c r="H2">
-        <v>0.01306265080289541</v>
+        <v>-0.02093002889920308</v>
       </c>
       <c r="I2">
-        <v>-0.0139778683750728</v>
+        <v>-0.03695595060863473</v>
       </c>
       <c r="J2">
-        <v>-0.0139778683750728</v>
+        <v>-0.03695595060863473</v>
       </c>
       <c r="K2">
-        <v>-45.2</v>
+        <v>-108.2</v>
       </c>
       <c r="L2">
-        <v>-0.03760712205674349</v>
+        <v>-0.09475435677379805</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>324.6</v>
+        <v>113</v>
       </c>
       <c r="V2">
-        <v>0.1398354370395899</v>
+        <v>0.1324736225087925</v>
       </c>
       <c r="W2">
-        <v>-0.1280453257790368</v>
+        <v>-0.2066857688634193</v>
       </c>
       <c r="X2">
-        <v>0.06275758551014519</v>
+        <v>0.108859515398654</v>
       </c>
       <c r="Y2">
-        <v>-0.190802911289182</v>
+        <v>-0.3155452842620733</v>
       </c>
       <c r="Z2">
-        <v>2.890572390572391</v>
+        <v>2.307801131770413</v>
       </c>
       <c r="AA2">
-        <v>-0.04040404040404041</v>
+        <v>-0.0852869846402587</v>
       </c>
       <c r="AB2">
-        <v>0.05803342491913323</v>
+        <v>0.09252617661711676</v>
       </c>
       <c r="AC2">
-        <v>-0.09843746532317363</v>
+        <v>-0.1778131612573755</v>
       </c>
       <c r="AD2">
-        <v>295.9</v>
+        <v>269.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>295.9</v>
+        <v>269.4</v>
       </c>
       <c r="AG2">
-        <v>-28.70000000000005</v>
+        <v>156.4</v>
       </c>
       <c r="AH2">
-        <v>0.1130597585205563</v>
+        <v>0.2400213827512473</v>
       </c>
       <c r="AI2">
-        <v>0.3611178911398584</v>
+        <v>0.4320769847634322</v>
       </c>
       <c r="AJ2">
-        <v>-0.01251853790456252</v>
+        <v>0.1549435308103824</v>
       </c>
       <c r="AK2">
-        <v>-0.05800323362974949</v>
+        <v>0.3063663075416258</v>
       </c>
       <c r="AL2">
-        <v>9.92</v>
+        <v>11.2</v>
       </c>
       <c r="AM2">
-        <v>9.92</v>
+        <v>9.209999999999999</v>
       </c>
       <c r="AN2">
-        <v>1771.85628742515</v>
+        <v>-12.35779816513761</v>
       </c>
       <c r="AO2">
-        <v>-1.693548387096774</v>
+        <v>-3.767857142857143</v>
       </c>
       <c r="AP2">
-        <v>-171.85628742515</v>
+        <v>-7.174311926605503</v>
       </c>
       <c r="AQ2">
-        <v>-1.693548387096774</v>
+        <v>-4.581976112920739</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.455</v>
+        <v>0.367</v>
       </c>
       <c r="G3">
-        <v>0.01306265080289541</v>
+        <v>-0.02093002889920308</v>
       </c>
       <c r="H3">
-        <v>0.01306265080289541</v>
+        <v>-0.02093002889920308</v>
       </c>
       <c r="I3">
-        <v>-0.0139778683750728</v>
+        <v>-0.03695595060863473</v>
       </c>
       <c r="J3">
-        <v>-0.0139778683750728</v>
+        <v>-0.03695595060863473</v>
       </c>
       <c r="K3">
-        <v>-45.2</v>
+        <v>-108.2</v>
       </c>
       <c r="L3">
-        <v>-0.03760712205674349</v>
+        <v>-0.09475435677379805</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>324.6</v>
+        <v>113</v>
       </c>
       <c r="V3">
-        <v>0.1398354370395899</v>
+        <v>0.1324736225087925</v>
       </c>
       <c r="W3">
-        <v>-0.1280453257790368</v>
+        <v>-0.2066857688634193</v>
       </c>
       <c r="X3">
-        <v>0.06275758551014519</v>
+        <v>0.108859515398654</v>
       </c>
       <c r="Y3">
-        <v>-0.190802911289182</v>
+        <v>-0.3155452842620733</v>
       </c>
       <c r="Z3">
-        <v>2.890572390572391</v>
+        <v>2.307801131770413</v>
       </c>
       <c r="AA3">
-        <v>-0.04040404040404041</v>
+        <v>-0.0852869846402587</v>
       </c>
       <c r="AB3">
-        <v>0.05803342491913323</v>
+        <v>0.09252617661711676</v>
       </c>
       <c r="AC3">
-        <v>-0.09843746532317363</v>
+        <v>-0.1778131612573755</v>
       </c>
       <c r="AD3">
-        <v>295.9</v>
+        <v>269.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>295.9</v>
+        <v>269.4</v>
       </c>
       <c r="AG3">
-        <v>-28.70000000000005</v>
+        <v>156.4</v>
       </c>
       <c r="AH3">
-        <v>0.1130597585205563</v>
+        <v>0.2400213827512473</v>
       </c>
       <c r="AI3">
-        <v>0.3611178911398584</v>
+        <v>0.4320769847634322</v>
       </c>
       <c r="AJ3">
-        <v>-0.01251853790456252</v>
+        <v>0.1549435308103824</v>
       </c>
       <c r="AK3">
-        <v>-0.05800323362974949</v>
+        <v>0.3063663075416258</v>
       </c>
       <c r="AL3">
-        <v>9.92</v>
+        <v>11.2</v>
       </c>
       <c r="AM3">
-        <v>9.92</v>
+        <v>9.209999999999999</v>
       </c>
       <c r="AN3">
-        <v>1771.85628742515</v>
+        <v>-12.35779816513761</v>
       </c>
       <c r="AO3">
-        <v>-1.693548387096774</v>
+        <v>-3.767857142857143</v>
       </c>
       <c r="AP3">
-        <v>-171.85628742515</v>
+        <v>-7.174311926605503</v>
       </c>
       <c r="AQ3">
-        <v>-1.693548387096774</v>
+        <v>-4.581976112920739</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_special_lines.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.367</v>
+        <v>0.271</v>
       </c>
       <c r="G2">
-        <v>-0.02093002889920308</v>
+        <v>-0.02149837133550488</v>
       </c>
       <c r="H2">
-        <v>-0.02093002889920308</v>
+        <v>-0.02149837133550488</v>
       </c>
       <c r="I2">
-        <v>-0.03695595060863473</v>
+        <v>-0.005116967722830915</v>
       </c>
       <c r="J2">
-        <v>-0.03695595060863473</v>
+        <v>-0.005116967722830915</v>
       </c>
       <c r="K2">
-        <v>-108.2</v>
+        <v>-17.2</v>
       </c>
       <c r="L2">
-        <v>-0.09475435677379805</v>
+        <v>-0.01018655611489488</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>113</v>
+        <v>160.6</v>
       </c>
       <c r="V2">
-        <v>0.1324736225087925</v>
+        <v>0.06066558380236467</v>
       </c>
       <c r="W2">
-        <v>-0.2066857688634193</v>
+        <v>-0.04857384919514261</v>
       </c>
       <c r="X2">
-        <v>0.108859515398654</v>
+        <v>0.08700704133521664</v>
       </c>
       <c r="Y2">
-        <v>-0.3155452842620733</v>
+        <v>-0.1355808905303593</v>
       </c>
       <c r="Z2">
-        <v>2.307801131770413</v>
+        <v>3.307541625857003</v>
       </c>
       <c r="AA2">
-        <v>-0.0852869846402587</v>
+        <v>-0.01692458374142997</v>
       </c>
       <c r="AB2">
-        <v>0.09252617661711676</v>
+        <v>0.08262220274363158</v>
       </c>
       <c r="AC2">
-        <v>-0.1778131612573755</v>
+        <v>-0.09954678648506154</v>
       </c>
       <c r="AD2">
-        <v>269.4</v>
+        <v>258.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>269.4</v>
+        <v>258.6</v>
       </c>
       <c r="AG2">
-        <v>156.4</v>
+        <v>98.00000000000003</v>
       </c>
       <c r="AH2">
-        <v>0.2400213827512473</v>
+        <v>0.0889913624006332</v>
       </c>
       <c r="AI2">
-        <v>0.4320769847634322</v>
+        <v>0.2801126516464472</v>
       </c>
       <c r="AJ2">
-        <v>0.1549435308103824</v>
+        <v>0.03569737369322115</v>
       </c>
       <c r="AK2">
-        <v>0.3063663075416258</v>
+        <v>0.1285077366902702</v>
       </c>
       <c r="AL2">
-        <v>11.2</v>
+        <v>7.98</v>
       </c>
       <c r="AM2">
-        <v>9.209999999999999</v>
+        <v>6.07</v>
       </c>
       <c r="AN2">
-        <v>-12.35779816513761</v>
+        <v>16.1625</v>
       </c>
       <c r="AO2">
-        <v>-3.767857142857143</v>
+        <v>-1.082706766917293</v>
       </c>
       <c r="AP2">
-        <v>-7.174311926605503</v>
+        <v>6.125000000000002</v>
       </c>
       <c r="AQ2">
-        <v>-4.581976112920739</v>
+        <v>-1.42339373970346</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shop Apotheke Europe N.V. (XTRA:SAE)</t>
+          <t>Redcare Pharmacy NV (XTRA:RDC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.367</v>
+        <v>0.271</v>
       </c>
       <c r="G3">
-        <v>-0.02093002889920308</v>
+        <v>-0.02149837133550488</v>
       </c>
       <c r="H3">
-        <v>-0.02093002889920308</v>
+        <v>-0.02149837133550488</v>
       </c>
       <c r="I3">
-        <v>-0.03695595060863473</v>
+        <v>-0.005116967722830915</v>
       </c>
       <c r="J3">
-        <v>-0.03695595060863473</v>
+        <v>-0.005116967722830915</v>
       </c>
       <c r="K3">
-        <v>-108.2</v>
+        <v>-17.2</v>
       </c>
       <c r="L3">
-        <v>-0.09475435677379805</v>
+        <v>-0.01018655611489488</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>113</v>
+        <v>160.6</v>
       </c>
       <c r="V3">
-        <v>0.1324736225087925</v>
+        <v>0.06066558380236467</v>
       </c>
       <c r="W3">
-        <v>-0.2066857688634193</v>
+        <v>-0.04857384919514261</v>
       </c>
       <c r="X3">
-        <v>0.108859515398654</v>
+        <v>0.08700704133521664</v>
       </c>
       <c r="Y3">
-        <v>-0.3155452842620733</v>
+        <v>-0.1355808905303593</v>
       </c>
       <c r="Z3">
-        <v>2.307801131770413</v>
+        <v>3.307541625857003</v>
       </c>
       <c r="AA3">
-        <v>-0.0852869846402587</v>
+        <v>-0.01692458374142997</v>
       </c>
       <c r="AB3">
-        <v>0.09252617661711676</v>
+        <v>0.08262220274363158</v>
       </c>
       <c r="AC3">
-        <v>-0.1778131612573755</v>
+        <v>-0.09954678648506154</v>
       </c>
       <c r="AD3">
-        <v>269.4</v>
+        <v>258.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>269.4</v>
+        <v>258.6</v>
       </c>
       <c r="AG3">
-        <v>156.4</v>
+        <v>98.00000000000003</v>
       </c>
       <c r="AH3">
-        <v>0.2400213827512473</v>
+        <v>0.0889913624006332</v>
       </c>
       <c r="AI3">
-        <v>0.4320769847634322</v>
+        <v>0.2801126516464472</v>
       </c>
       <c r="AJ3">
-        <v>0.1549435308103824</v>
+        <v>0.03569737369322115</v>
       </c>
       <c r="AK3">
-        <v>0.3063663075416258</v>
+        <v>0.1285077366902702</v>
       </c>
       <c r="AL3">
-        <v>11.2</v>
+        <v>7.98</v>
       </c>
       <c r="AM3">
-        <v>9.209999999999999</v>
+        <v>6.07</v>
       </c>
       <c r="AN3">
-        <v>-12.35779816513761</v>
+        <v>16.1625</v>
       </c>
       <c r="AO3">
-        <v>-3.767857142857143</v>
+        <v>-1.082706766917293</v>
       </c>
       <c r="AP3">
-        <v>-7.174311926605503</v>
+        <v>6.125000000000002</v>
       </c>
       <c r="AQ3">
-        <v>-4.581976112920739</v>
+        <v>-1.42339373970346</v>
       </c>
     </row>
   </sheetData>
